--- a/artfynd/A 39376-2023 artfynd.xlsx
+++ b/artfynd/A 39376-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,59 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112680534</v>
+        <v>137106652</v>
       </c>
       <c r="B2" t="n">
-        <v>87289</v>
+        <v>87421</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>473</v>
+        <v>445</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bon</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mattsarve, Gtl</t>
+          <t>Uppstaig, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>728283</v>
+        <v>728330</v>
       </c>
       <c r="R2" t="n">
-        <v>6371840</v>
+        <v>6371692</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,88 +769,71 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Ängsgranskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112680534</t>
+          <t>https://artportalen.se/Sighting/137106652</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113868234</v>
+        <v>137124493</v>
       </c>
       <c r="B3" t="n">
-        <v>91680</v>
+        <v>87421</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>445</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelgarn Mattsarve vid Uppstaig, Gtl</t>
+          <t>Uppstaig, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>728342</v>
+        <v>728334</v>
       </c>
       <c r="R3" t="n">
-        <v>6371738</v>
+        <v>6371756</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,12 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,75 +881,71 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Nygren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Nygren</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113868234</t>
+          <t>https://artportalen.se/Sighting/137124493</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112680545</v>
+        <v>137124490</v>
       </c>
       <c r="B4" t="n">
-        <v>91361</v>
+        <v>87551</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3286</v>
+        <v>449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mattsarve, Gtl</t>
+          <t>Uppstaig, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>728433</v>
+        <v>728308</v>
       </c>
       <c r="R4" t="n">
-        <v>6371706</v>
+        <v>6371682</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,12 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,83 +993,71 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112680545</t>
+          <t>https://artportalen.se/Sighting/137124490</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113868322</v>
+        <v>137124492</v>
       </c>
       <c r="B5" t="n">
-        <v>91361</v>
+        <v>87551</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3286</v>
+        <v>449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gammelgarn Mattsarve vid Uppstaig, Gtl</t>
+          <t>Uppstaig, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>728207</v>
+        <v>728344</v>
       </c>
       <c r="R5" t="n">
-        <v>6371872</v>
+        <v>6371754</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,12 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,56 +1105,55 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia Nygren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Nygren</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113868322</t>
+          <t>https://artportalen.se/Sighting/137124492</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113868403</v>
+        <v>112680534</v>
       </c>
       <c r="B6" t="n">
-        <v>87309</v>
+        <v>87289</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3674</v>
+        <v>473</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1175,17 +1170,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gammelgarn Mattsarve vid Uppstaig, Gtl</t>
+          <t>Mattsarve, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>728213</v>
+        <v>728283</v>
       </c>
       <c r="R6" t="n">
-        <v>6371873</v>
+        <v>6371840</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,12 +1204,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,57 +1222,62 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Ängsgranskog</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cecilia Nygren</t>
+          <t>Ingrid Thomasson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Nygren</t>
+          <t>Ingrid Thomasson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113868403</t>
+          <t>https://artportalen.se/Sighting/112680534</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113868297</v>
+        <v>113868234</v>
       </c>
       <c r="B7" t="n">
-        <v>87170</v>
+        <v>91680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3712</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>728208</v>
+        <v>728342</v>
       </c>
       <c r="R7" t="n">
-        <v>6371866</v>
+        <v>6371738</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1355,16 +1355,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113868297</t>
+          <t>https://artportalen.se/Sighting/113868234</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113868213</v>
+        <v>112680545</v>
       </c>
       <c r="B8" t="n">
-        <v>75428</v>
+        <v>91361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,48 +1372,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>3286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelgarn Mattsarve vid Uppstaig, Gtl</t>
+          <t>Mattsarve, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>728342</v>
+        <v>728433</v>
       </c>
       <c r="R8" t="n">
-        <v>6371738</v>
+        <v>6371706</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,12 +1429,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,49 +1450,49 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Nygren</t>
+          <t>Ingrid Thomasson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Nygren</t>
+          <t>Ingrid Thomasson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113868213</t>
+          <t>https://artportalen.se/Sighting/112680545</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113869483</v>
+        <v>113868322</v>
       </c>
       <c r="B9" t="n">
-        <v>99096</v>
+        <v>91361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>3286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1510,11 +1502,10 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1522,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>728401</v>
+        <v>728207</v>
       </c>
       <c r="R9" t="n">
-        <v>6371719</v>
+        <v>6371872</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1584,66 +1575,54 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113869483</t>
+          <t>https://artportalen.se/Sighting/113868322</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113869518</v>
+        <v>137124500</v>
       </c>
       <c r="B10" t="n">
-        <v>99096</v>
+        <v>87516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>3599</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gammelgarn Mattsarve vid Uppstaig, Gtl</t>
+          <t>Uppstaig, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>728379</v>
+        <v>728258</v>
       </c>
       <c r="R10" t="n">
-        <v>6371711</v>
+        <v>6371845</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1667,12 +1646,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,54 +1677,54 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Nygren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Nygren</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113869518</t>
+          <t>https://artportalen.se/Sighting/137124500</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113869302</v>
+        <v>113868403</v>
       </c>
       <c r="B11" t="n">
-        <v>87346</v>
+        <v>87309</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1813,62 +1802,51 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113869302</t>
+          <t>https://artportalen.se/Sighting/113868403</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113869505</v>
+        <v>137106650</v>
       </c>
       <c r="B12" t="n">
-        <v>87312</v>
+        <v>87492</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6037417</v>
+        <v>3674</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gammelgarn Mattsarve vid Uppstaig, Gtl</t>
+          <t>Uppstaig, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>728398</v>
+        <v>728269</v>
       </c>
       <c r="R12" t="n">
-        <v>6371713</v>
+        <v>6371618</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1895,12 +1873,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1909,23 +1897,2398 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Nygren</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Nygren</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137106650</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>113868297</v>
+      </c>
+      <c r="B13" t="n">
+        <v>87170</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gammelgarn Mattsarve vid Uppstaig, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>728208</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6371866</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113868297</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137106653</v>
+      </c>
+      <c r="B14" t="n">
+        <v>87353</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Uppstaig, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>728384</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6371680</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137106653</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137106654</v>
+      </c>
+      <c r="B15" t="n">
+        <v>87353</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Uppstaig, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>728404</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6371666</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137106654</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137106655</v>
+      </c>
+      <c r="B16" t="n">
+        <v>87353</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Uppstaig, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>728408</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6371664</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137106655</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137106657</v>
+      </c>
+      <c r="B17" t="n">
+        <v>87353</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Uppstaig, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>728424</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6371691</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137106657</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137106660</v>
+      </c>
+      <c r="B18" t="n">
+        <v>87353</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Uppstaig, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>728371</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6371598</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137106660</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137124488</v>
+      </c>
+      <c r="B19" t="n">
+        <v>87558</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Uppstaig, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>728307</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6371681</v>
+      </c>
+      <c r="S19" t="n">
+        <v>12</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124488</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137124491</v>
+      </c>
+      <c r="B20" t="n">
+        <v>87558</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Uppstaig, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>728312</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6371698</v>
+      </c>
+      <c r="S20" t="n">
+        <v>13</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124491</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137106658</v>
+      </c>
+      <c r="B21" t="n">
+        <v>87329</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Uppstaig, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>728427</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6371682</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137106658</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137124494</v>
+      </c>
+      <c r="B22" t="n">
+        <v>93428</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Uppstaig, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>728320</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6371744</v>
+      </c>
+      <c r="S22" t="n">
+        <v>11</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124494</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137106651</v>
+      </c>
+      <c r="B23" t="n">
+        <v>93088</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Uppstaig, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>728283</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6371650</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137106651</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137124497</v>
+      </c>
+      <c r="B24" t="n">
+        <v>93088</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Uppstaig, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>728255</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6371726</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124497</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137124499</v>
+      </c>
+      <c r="B25" t="n">
+        <v>93088</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Uppstaig, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>728268</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6371831</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124499</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137106659</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93452</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Uppstaig, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>728422</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6371655</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137106659</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>113868213</v>
+      </c>
+      <c r="B27" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gammelgarn Mattsarve vid Uppstaig, Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>728342</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6371738</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Cecilia Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Cecilia Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113868213</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137124498</v>
+      </c>
+      <c r="B28" t="n">
+        <v>8452</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Uppstaig, Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>728250</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6371732</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124498</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>113869483</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gammelgarn Mattsarve vid Uppstaig, Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>728401</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6371719</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Cecilia Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Cecilia Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113869483</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>113869518</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gammelgarn Mattsarve vid Uppstaig, Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>728379</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6371711</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Cecilia Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Cecilia Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113869518</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>113869302</v>
+      </c>
+      <c r="B31" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gammelgarn Mattsarve vid Uppstaig, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>728213</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6371873</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Cecilia Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Cecilia Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113869302</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137106661</v>
+      </c>
+      <c r="B32" t="n">
+        <v>87529</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Uppstaig, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>728384</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6371513</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137106661</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>113869505</v>
+      </c>
+      <c r="B33" t="n">
+        <v>87312</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6037417</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Denisespindling</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gammelgarn Mattsarve vid Uppstaig, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>728398</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6371713</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Gammelgarn</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Cecilia Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Cecilia Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/113869505</t>
         </is>
@@ -1944,6 +4307,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39376-2023 artfynd.xlsx
+++ b/artfynd/A 39376-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106652</v>
       </c>
       <c r="B2" t="n">
-        <v>87421</v>
+        <v>87427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124493</v>
       </c>
       <c r="B3" t="n">
-        <v>87421</v>
+        <v>87427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124490</v>
       </c>
       <c r="B4" t="n">
-        <v>87551</v>
+        <v>87557</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137124492</v>
       </c>
       <c r="B5" t="n">
-        <v>87551</v>
+        <v>87557</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137124500</v>
       </c>
       <c r="B10" t="n">
-        <v>87516</v>
+        <v>87522</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>137106650</v>
       </c>
       <c r="B12" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>137106653</v>
       </c>
       <c r="B14" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>137106654</v>
       </c>
       <c r="B15" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>137106655</v>
       </c>
       <c r="B16" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137106657</v>
       </c>
       <c r="B17" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>137106660</v>
       </c>
       <c r="B18" t="n">
-        <v>87353</v>
+        <v>87359</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>137124488</v>
       </c>
       <c r="B19" t="n">
-        <v>87558</v>
+        <v>87564</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>137124491</v>
       </c>
       <c r="B20" t="n">
-        <v>87558</v>
+        <v>87564</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137106658</v>
       </c>
       <c r="B21" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>137124494</v>
       </c>
       <c r="B22" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>137106651</v>
       </c>
       <c r="B23" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>137124497</v>
       </c>
       <c r="B24" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>137124499</v>
       </c>
       <c r="B25" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>137106659</v>
       </c>
       <c r="B26" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>137106661</v>
       </c>
       <c r="B32" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 39376-2023 artfynd.xlsx
+++ b/artfynd/A 39376-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106652</v>
       </c>
       <c r="B2" t="n">
-        <v>87427</v>
+        <v>87431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124493</v>
       </c>
       <c r="B3" t="n">
-        <v>87427</v>
+        <v>87431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124490</v>
       </c>
       <c r="B4" t="n">
-        <v>87557</v>
+        <v>87561</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137124492</v>
       </c>
       <c r="B5" t="n">
-        <v>87557</v>
+        <v>87561</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137124500</v>
       </c>
       <c r="B10" t="n">
-        <v>87522</v>
+        <v>87526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>137106650</v>
       </c>
       <c r="B12" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>137106653</v>
       </c>
       <c r="B14" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>137106654</v>
       </c>
       <c r="B15" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>137106655</v>
       </c>
       <c r="B16" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137106657</v>
       </c>
       <c r="B17" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>137106660</v>
       </c>
       <c r="B18" t="n">
-        <v>87359</v>
+        <v>87363</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>137124488</v>
       </c>
       <c r="B19" t="n">
-        <v>87564</v>
+        <v>87568</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>728307</v>
+        <v>728308</v>
       </c>
       <c r="R19" t="n">
         <v>6371681</v>
@@ -2709,7 +2709,7 @@
         <v>137124491</v>
       </c>
       <c r="B20" t="n">
-        <v>87564</v>
+        <v>87568</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137106658</v>
       </c>
       <c r="B21" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>137124494</v>
       </c>
       <c r="B22" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>137106651</v>
       </c>
       <c r="B23" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>137124497</v>
       </c>
       <c r="B24" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>137124499</v>
       </c>
       <c r="B25" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>137106659</v>
       </c>
       <c r="B26" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>137106661</v>
       </c>
       <c r="B32" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 39376-2023 artfynd.xlsx
+++ b/artfynd/A 39376-2023 artfynd.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>728308</v>
+        <v>728307</v>
       </c>
       <c r="R19" t="n">
         <v>6371681</v>

--- a/artfynd/A 39376-2023 artfynd.xlsx
+++ b/artfynd/A 39376-2023 artfynd.xlsx
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>728307</v>
+        <v>728308</v>
       </c>
       <c r="R19" t="n">
         <v>6371681</v>

--- a/artfynd/A 39376-2023 artfynd.xlsx
+++ b/artfynd/A 39376-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106652</v>
       </c>
       <c r="B2" t="n">
-        <v>87431</v>
+        <v>87433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124493</v>
       </c>
       <c r="B3" t="n">
-        <v>87431</v>
+        <v>87433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124490</v>
       </c>
       <c r="B4" t="n">
-        <v>87561</v>
+        <v>87563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137124492</v>
       </c>
       <c r="B5" t="n">
-        <v>87561</v>
+        <v>87563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137124500</v>
       </c>
       <c r="B10" t="n">
-        <v>87526</v>
+        <v>87528</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>137106650</v>
       </c>
       <c r="B12" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>137106653</v>
       </c>
       <c r="B14" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>137106654</v>
       </c>
       <c r="B15" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>137106655</v>
       </c>
       <c r="B16" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137106657</v>
       </c>
       <c r="B17" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>137106660</v>
       </c>
       <c r="B18" t="n">
-        <v>87363</v>
+        <v>87365</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>137124488</v>
       </c>
       <c r="B19" t="n">
-        <v>87568</v>
+        <v>87570</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>728308</v>
+        <v>728307</v>
       </c>
       <c r="R19" t="n">
         <v>6371681</v>
@@ -2709,7 +2709,7 @@
         <v>137124491</v>
       </c>
       <c r="B20" t="n">
-        <v>87568</v>
+        <v>87570</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137106658</v>
       </c>
       <c r="B21" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>137124494</v>
       </c>
       <c r="B22" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>137106651</v>
       </c>
       <c r="B23" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>137124497</v>
       </c>
       <c r="B24" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>137124499</v>
       </c>
       <c r="B25" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>137106659</v>
       </c>
       <c r="B26" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>137106661</v>
       </c>
       <c r="B32" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 39376-2023 artfynd.xlsx
+++ b/artfynd/A 39376-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106652</v>
       </c>
       <c r="B2" t="n">
-        <v>87433</v>
+        <v>87446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124493</v>
       </c>
       <c r="B3" t="n">
-        <v>87433</v>
+        <v>87446</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124490</v>
       </c>
       <c r="B4" t="n">
-        <v>87563</v>
+        <v>87576</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137124492</v>
       </c>
       <c r="B5" t="n">
-        <v>87563</v>
+        <v>87576</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137124500</v>
       </c>
       <c r="B10" t="n">
-        <v>87528</v>
+        <v>87541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>137106650</v>
       </c>
       <c r="B12" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>137106653</v>
       </c>
       <c r="B14" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>137106654</v>
       </c>
       <c r="B15" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>137106655</v>
       </c>
       <c r="B16" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137106657</v>
       </c>
       <c r="B17" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>137106660</v>
       </c>
       <c r="B18" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>137124488</v>
       </c>
       <c r="B19" t="n">
-        <v>87570</v>
+        <v>87583</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>728307</v>
+        <v>728308</v>
       </c>
       <c r="R19" t="n">
         <v>6371681</v>
@@ -2709,7 +2709,7 @@
         <v>137124491</v>
       </c>
       <c r="B20" t="n">
-        <v>87570</v>
+        <v>87583</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137106658</v>
       </c>
       <c r="B21" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>137124494</v>
       </c>
       <c r="B22" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>137106651</v>
       </c>
       <c r="B23" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>137124497</v>
       </c>
       <c r="B24" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>137124499</v>
       </c>
       <c r="B25" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>137106659</v>
       </c>
       <c r="B26" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>137106661</v>
       </c>
       <c r="B32" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 39376-2023 artfynd.xlsx
+++ b/artfynd/A 39376-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106652</v>
       </c>
       <c r="B2" t="n">
-        <v>87446</v>
+        <v>87448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124493</v>
       </c>
       <c r="B3" t="n">
-        <v>87446</v>
+        <v>87448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124490</v>
       </c>
       <c r="B4" t="n">
-        <v>87576</v>
+        <v>87578</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137124492</v>
       </c>
       <c r="B5" t="n">
-        <v>87576</v>
+        <v>87578</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137124500</v>
       </c>
       <c r="B10" t="n">
-        <v>87541</v>
+        <v>87543</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>137106650</v>
       </c>
       <c r="B12" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>137106653</v>
       </c>
       <c r="B14" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>137106654</v>
       </c>
       <c r="B15" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>137106655</v>
       </c>
       <c r="B16" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137106657</v>
       </c>
       <c r="B17" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>137106660</v>
       </c>
       <c r="B18" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>137124488</v>
       </c>
       <c r="B19" t="n">
-        <v>87583</v>
+        <v>87585</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>137124491</v>
       </c>
       <c r="B20" t="n">
-        <v>87583</v>
+        <v>87585</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137106658</v>
       </c>
       <c r="B21" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>137124494</v>
       </c>
       <c r="B22" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>137106651</v>
       </c>
       <c r="B23" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>137124497</v>
       </c>
       <c r="B24" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>137124499</v>
       </c>
       <c r="B25" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>137106659</v>
       </c>
       <c r="B26" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>137124498</v>
       </c>
       <c r="B28" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>137106661</v>
       </c>
       <c r="B32" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 39376-2023 artfynd.xlsx
+++ b/artfynd/A 39376-2023 artfynd.xlsx
@@ -3636,11 +3636,7 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>

--- a/artfynd/A 39376-2023 artfynd.xlsx
+++ b/artfynd/A 39376-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106652</v>
       </c>
       <c r="B2" t="n">
-        <v>87448</v>
+        <v>87451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124493</v>
       </c>
       <c r="B3" t="n">
-        <v>87448</v>
+        <v>87451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124490</v>
       </c>
       <c r="B4" t="n">
-        <v>87578</v>
+        <v>87581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137124492</v>
       </c>
       <c r="B5" t="n">
-        <v>87578</v>
+        <v>87581</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137124500</v>
       </c>
       <c r="B10" t="n">
-        <v>87543</v>
+        <v>87546</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>137106650</v>
       </c>
       <c r="B12" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>137106653</v>
       </c>
       <c r="B14" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>137106654</v>
       </c>
       <c r="B15" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>137106655</v>
       </c>
       <c r="B16" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137106657</v>
       </c>
       <c r="B17" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>137106660</v>
       </c>
       <c r="B18" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>137124488</v>
       </c>
       <c r="B19" t="n">
-        <v>87585</v>
+        <v>87588</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>728308</v>
+        <v>728307</v>
       </c>
       <c r="R19" t="n">
         <v>6371681</v>
@@ -2709,7 +2709,7 @@
         <v>137124491</v>
       </c>
       <c r="B20" t="n">
-        <v>87585</v>
+        <v>87588</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137106658</v>
       </c>
       <c r="B21" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>137124494</v>
       </c>
       <c r="B22" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>137106651</v>
       </c>
       <c r="B23" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>137124497</v>
       </c>
       <c r="B24" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>137124499</v>
       </c>
       <c r="B25" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>137106659</v>
       </c>
       <c r="B26" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>137106661</v>
       </c>
       <c r="B32" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 39376-2023 artfynd.xlsx
+++ b/artfynd/A 39376-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106652</v>
       </c>
       <c r="B2" t="n">
-        <v>87451</v>
+        <v>87461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124493</v>
       </c>
       <c r="B3" t="n">
-        <v>87451</v>
+        <v>87461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124490</v>
       </c>
       <c r="B4" t="n">
-        <v>87581</v>
+        <v>87591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137124492</v>
       </c>
       <c r="B5" t="n">
-        <v>87581</v>
+        <v>87591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137124500</v>
       </c>
       <c r="B10" t="n">
-        <v>87546</v>
+        <v>87556</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>137106650</v>
       </c>
       <c r="B12" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>137106653</v>
       </c>
       <c r="B14" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>137106654</v>
       </c>
       <c r="B15" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>137106655</v>
       </c>
       <c r="B16" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137106657</v>
       </c>
       <c r="B17" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>137106660</v>
       </c>
       <c r="B18" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>137124488</v>
       </c>
       <c r="B19" t="n">
-        <v>87588</v>
+        <v>87598</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>137124491</v>
       </c>
       <c r="B20" t="n">
-        <v>87588</v>
+        <v>87598</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137106658</v>
       </c>
       <c r="B21" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>137124494</v>
       </c>
       <c r="B22" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>137106651</v>
       </c>
       <c r="B23" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>137124497</v>
       </c>
       <c r="B24" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>137124499</v>
       </c>
       <c r="B25" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>137106659</v>
       </c>
       <c r="B26" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>137124498</v>
       </c>
       <c r="B28" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>137106661</v>
       </c>
       <c r="B32" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 39376-2023 artfynd.xlsx
+++ b/artfynd/A 39376-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106652</v>
       </c>
       <c r="B2" t="n">
-        <v>87461</v>
+        <v>87462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124493</v>
       </c>
       <c r="B3" t="n">
-        <v>87461</v>
+        <v>87462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124490</v>
       </c>
       <c r="B4" t="n">
-        <v>87591</v>
+        <v>87592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137124492</v>
       </c>
       <c r="B5" t="n">
-        <v>87591</v>
+        <v>87592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137124500</v>
       </c>
       <c r="B10" t="n">
-        <v>87556</v>
+        <v>87557</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>137106650</v>
       </c>
       <c r="B12" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>137106653</v>
       </c>
       <c r="B14" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>137106654</v>
       </c>
       <c r="B15" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>137106655</v>
       </c>
       <c r="B16" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137106657</v>
       </c>
       <c r="B17" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>137106660</v>
       </c>
       <c r="B18" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>137124488</v>
       </c>
       <c r="B19" t="n">
-        <v>87598</v>
+        <v>87599</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>137124491</v>
       </c>
       <c r="B20" t="n">
-        <v>87598</v>
+        <v>87599</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137106658</v>
       </c>
       <c r="B21" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>137124494</v>
       </c>
       <c r="B22" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>137106651</v>
       </c>
       <c r="B23" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>137124497</v>
       </c>
       <c r="B24" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>137124499</v>
       </c>
       <c r="B25" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>137106659</v>
       </c>
       <c r="B26" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>137106661</v>
       </c>
       <c r="B32" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 39376-2023 artfynd.xlsx
+++ b/artfynd/A 39376-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106652</v>
       </c>
       <c r="B2" t="n">
-        <v>87462</v>
+        <v>87465</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124493</v>
       </c>
       <c r="B3" t="n">
-        <v>87462</v>
+        <v>87465</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124490</v>
       </c>
       <c r="B4" t="n">
-        <v>87592</v>
+        <v>87595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137124492</v>
       </c>
       <c r="B5" t="n">
-        <v>87592</v>
+        <v>87595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137124500</v>
       </c>
       <c r="B10" t="n">
-        <v>87557</v>
+        <v>87560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>137106650</v>
       </c>
       <c r="B12" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>137106653</v>
       </c>
       <c r="B14" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>137106654</v>
       </c>
       <c r="B15" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>137106655</v>
       </c>
       <c r="B16" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137106657</v>
       </c>
       <c r="B17" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>137106660</v>
       </c>
       <c r="B18" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>137124488</v>
       </c>
       <c r="B19" t="n">
-        <v>87599</v>
+        <v>87602</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>137124491</v>
       </c>
       <c r="B20" t="n">
-        <v>87599</v>
+        <v>87602</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137106658</v>
       </c>
       <c r="B21" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>137124494</v>
       </c>
       <c r="B22" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>137106651</v>
       </c>
       <c r="B23" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>137124497</v>
       </c>
       <c r="B24" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>137124499</v>
       </c>
       <c r="B25" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>137106659</v>
       </c>
       <c r="B26" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>137106661</v>
       </c>
       <c r="B32" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 39376-2023 artfynd.xlsx
+++ b/artfynd/A 39376-2023 artfynd.xlsx
@@ -2933,7 +2933,7 @@
         <v>137124494</v>
       </c>
       <c r="B22" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>137106651</v>
       </c>
       <c r="B23" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>137124497</v>
       </c>
       <c r="B24" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>137124499</v>
       </c>
       <c r="B25" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>137106659</v>
       </c>
       <c r="B26" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 39376-2023 artfynd.xlsx
+++ b/artfynd/A 39376-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106652</v>
       </c>
       <c r="B2" t="n">
-        <v>87465</v>
+        <v>87470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124493</v>
       </c>
       <c r="B3" t="n">
-        <v>87465</v>
+        <v>87470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124490</v>
       </c>
       <c r="B4" t="n">
-        <v>87595</v>
+        <v>87600</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137124492</v>
       </c>
       <c r="B5" t="n">
-        <v>87595</v>
+        <v>87600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137124500</v>
       </c>
       <c r="B10" t="n">
-        <v>87560</v>
+        <v>87565</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>137106650</v>
       </c>
       <c r="B12" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>137106653</v>
       </c>
       <c r="B14" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>137106654</v>
       </c>
       <c r="B15" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>137106655</v>
       </c>
       <c r="B16" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137106657</v>
       </c>
       <c r="B17" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>137106660</v>
       </c>
       <c r="B18" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>137124488</v>
       </c>
       <c r="B19" t="n">
-        <v>87602</v>
+        <v>87607</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>137124491</v>
       </c>
       <c r="B20" t="n">
-        <v>87602</v>
+        <v>87607</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137106658</v>
       </c>
       <c r="B21" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>137124494</v>
       </c>
       <c r="B22" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>137106651</v>
       </c>
       <c r="B23" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>137124497</v>
       </c>
       <c r="B24" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>137124499</v>
       </c>
       <c r="B25" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>137106659</v>
       </c>
       <c r="B26" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>137106661</v>
       </c>
       <c r="B32" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 39376-2023 artfynd.xlsx
+++ b/artfynd/A 39376-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106652</v>
       </c>
       <c r="B2" t="n">
-        <v>87470</v>
+        <v>87481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124493</v>
       </c>
       <c r="B3" t="n">
-        <v>87470</v>
+        <v>87481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124490</v>
       </c>
       <c r="B4" t="n">
-        <v>87600</v>
+        <v>87611</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137124492</v>
       </c>
       <c r="B5" t="n">
-        <v>87600</v>
+        <v>87611</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137124500</v>
       </c>
       <c r="B10" t="n">
-        <v>87565</v>
+        <v>87576</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>137106650</v>
       </c>
       <c r="B12" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>137106653</v>
       </c>
       <c r="B14" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>137106654</v>
       </c>
       <c r="B15" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>137106655</v>
       </c>
       <c r="B16" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137106657</v>
       </c>
       <c r="B17" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>137106660</v>
       </c>
       <c r="B18" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>137124488</v>
       </c>
       <c r="B19" t="n">
-        <v>87607</v>
+        <v>87618</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>137124491</v>
       </c>
       <c r="B20" t="n">
-        <v>87607</v>
+        <v>87618</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137106658</v>
       </c>
       <c r="B21" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>137124494</v>
       </c>
       <c r="B22" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>137106651</v>
       </c>
       <c r="B23" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>137124497</v>
       </c>
       <c r="B24" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>137124499</v>
       </c>
       <c r="B25" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>137106659</v>
       </c>
       <c r="B26" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>137106661</v>
       </c>
       <c r="B32" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 39376-2023 artfynd.xlsx
+++ b/artfynd/A 39376-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106652</v>
       </c>
       <c r="B2" t="n">
-        <v>87481</v>
+        <v>87482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124493</v>
       </c>
       <c r="B3" t="n">
-        <v>87481</v>
+        <v>87482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124490</v>
       </c>
       <c r="B4" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137124492</v>
       </c>
       <c r="B5" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137124500</v>
       </c>
       <c r="B10" t="n">
-        <v>87576</v>
+        <v>87577</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>137106650</v>
       </c>
       <c r="B12" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>137106653</v>
       </c>
       <c r="B14" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>137106654</v>
       </c>
       <c r="B15" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>137106655</v>
       </c>
       <c r="B16" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137106657</v>
       </c>
       <c r="B17" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>137106660</v>
       </c>
       <c r="B18" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>137124488</v>
       </c>
       <c r="B19" t="n">
-        <v>87618</v>
+        <v>87619</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>728307</v>
+        <v>728308</v>
       </c>
       <c r="R19" t="n">
         <v>6371681</v>
@@ -2709,7 +2709,7 @@
         <v>137124491</v>
       </c>
       <c r="B20" t="n">
-        <v>87618</v>
+        <v>87619</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137106658</v>
       </c>
       <c r="B21" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>137124494</v>
       </c>
       <c r="B22" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>137106651</v>
       </c>
       <c r="B23" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>137124497</v>
       </c>
       <c r="B24" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>137124499</v>
       </c>
       <c r="B25" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>137106659</v>
       </c>
       <c r="B26" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>137106661</v>
       </c>
       <c r="B32" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 39376-2023 artfynd.xlsx
+++ b/artfynd/A 39376-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106652</v>
       </c>
       <c r="B2" t="n">
-        <v>87482</v>
+        <v>87485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124493</v>
       </c>
       <c r="B3" t="n">
-        <v>87482</v>
+        <v>87485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124490</v>
       </c>
       <c r="B4" t="n">
-        <v>87612</v>
+        <v>87615</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137124492</v>
       </c>
       <c r="B5" t="n">
-        <v>87612</v>
+        <v>87615</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137124500</v>
       </c>
       <c r="B10" t="n">
-        <v>87577</v>
+        <v>87580</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>137106650</v>
       </c>
       <c r="B12" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>137106653</v>
       </c>
       <c r="B14" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>137106654</v>
       </c>
       <c r="B15" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>137106655</v>
       </c>
       <c r="B16" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137106657</v>
       </c>
       <c r="B17" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>137106660</v>
       </c>
       <c r="B18" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>137124488</v>
       </c>
       <c r="B19" t="n">
-        <v>87619</v>
+        <v>87622</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>728308</v>
+        <v>728307</v>
       </c>
       <c r="R19" t="n">
         <v>6371681</v>
@@ -2709,7 +2709,7 @@
         <v>137124491</v>
       </c>
       <c r="B20" t="n">
-        <v>87619</v>
+        <v>87622</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137106658</v>
       </c>
       <c r="B21" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>137124494</v>
       </c>
       <c r="B22" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>137106651</v>
       </c>
       <c r="B23" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>137124497</v>
       </c>
       <c r="B24" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>137124499</v>
       </c>
       <c r="B25" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>137106659</v>
       </c>
       <c r="B26" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>137106661</v>
       </c>
       <c r="B32" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 39376-2023 artfynd.xlsx
+++ b/artfynd/A 39376-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137106652</v>
       </c>
       <c r="B2" t="n">
-        <v>87485</v>
+        <v>87489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124493</v>
       </c>
       <c r="B3" t="n">
-        <v>87485</v>
+        <v>87489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137124490</v>
       </c>
       <c r="B4" t="n">
-        <v>87615</v>
+        <v>87619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137124492</v>
       </c>
       <c r="B5" t="n">
-        <v>87615</v>
+        <v>87619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137124500</v>
       </c>
       <c r="B10" t="n">
-        <v>87580</v>
+        <v>87584</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>137106650</v>
       </c>
       <c r="B12" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>137106653</v>
       </c>
       <c r="B14" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>137106654</v>
       </c>
       <c r="B15" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>137106655</v>
       </c>
       <c r="B16" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137106657</v>
       </c>
       <c r="B17" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>137106660</v>
       </c>
       <c r="B18" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>137124488</v>
       </c>
       <c r="B19" t="n">
-        <v>87622</v>
+        <v>87626</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>137124491</v>
       </c>
       <c r="B20" t="n">
-        <v>87622</v>
+        <v>87626</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>137106658</v>
       </c>
       <c r="B21" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>137124494</v>
       </c>
       <c r="B22" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>137106651</v>
       </c>
       <c r="B23" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>137124497</v>
       </c>
       <c r="B24" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>137124499</v>
       </c>
       <c r="B25" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>137106659</v>
       </c>
       <c r="B26" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>137106661</v>
       </c>
       <c r="B32" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
